--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,8 +446,11 @@
           <t>行标记</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>a</t>
@@ -471,16 +474,19 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31日</t>
+          <t>2024年 12 月 31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024 年 9 月 30 日</t>
+          <t>2024 年 9 月 30 词讼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -496,8 +502,11 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -505,6 +514,8 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,29 +523,23 @@
           <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3,165,549</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3,124,043</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3,038,387</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3,045,754</t>
-        </is>
+      <c r="B5" t="n">
+        <v>3165549</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3124043</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3038387</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3045754</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -542,29 +547,23 @@
           <t>可用资本(数额)&gt;&gt;一级资本净额</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3,324,424</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3,322,954</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3,237,254</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3,245,824</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3324424</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3322954</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3237254</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3245824</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -572,31 +571,26 @@
           <t>可用资本(数额)&gt;&gt;资本净额</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4,303,263</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4,285,564</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4,175,087</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4,175,290</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4303263</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4285564</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4175087</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4175290</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -604,6 +598,8 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -611,29 +607,23 @@
           <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21,854,590</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>22,150,555</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>21,690,492</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>21,586,165</t>
-        </is>
+      <c r="B9" t="n">
+        <v>21854590</v>
+      </c>
+      <c r="C9" t="n">
+        <v>22150555</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21690492</v>
+      </c>
+      <c r="E9" t="n">
+        <v>21586165</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -641,31 +631,26 @@
           <t>风险加权资产(数额)&gt;&gt;风险加权资产合计(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>21,854,590</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>22,150,555</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21,690,492</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>21,586,165</t>
-        </is>
+      <c r="B10" t="n">
+        <v>21854590</v>
+      </c>
+      <c r="C10" t="n">
+        <v>22150555</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21690492</v>
+      </c>
+      <c r="E10" t="n">
+        <v>21586165</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -673,6 +658,8 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -680,29 +667,23 @@
           <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>14.10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
+      <c r="B12" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="C12" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14.11</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -710,29 +691,23 @@
           <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14.10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
+      <c r="B13" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="C13" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="E13" t="n">
+        <v>14.11</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -740,29 +715,23 @@
           <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
+      <c r="B14" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15.04</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -770,29 +739,23 @@
           <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
+      <c r="B15" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15.04</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -800,29 +763,23 @@
           <t>资本充足率&gt;&gt;资本充足率(%)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
+      <c r="B16" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>19.34</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -830,31 +787,26 @@
           <t>资本充足率&gt;&gt;资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
+      <c r="B17" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="C17" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>19.34</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -862,6 +814,8 @@
       <c r="F18" t="n">
         <v>0</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -869,29 +823,23 @@
           <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.5</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -899,29 +847,23 @@
           <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -929,29 +871,23 @@
           <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.5</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -959,29 +895,23 @@
           <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -989,31 +919,26 @@
           <t>其他各级资本要求&gt;&gt;满足最低资本要求后的可用核心一级资本净额占风险加权资产的比例(%)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>9.21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>8.92</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>9.04</t>
-        </is>
+      <c r="B23" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9.039999999999999</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -1021,6 +946,8 @@
       <c r="F24" t="n">
         <v>0</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1045,6 +972,68 @@
           <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1061,7 +1050,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
           <t>2024年&gt;&gt;12月31日</t>
@@ -1289,10 +1277,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>0</v>
       </c>
@@ -1388,10 +1372,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>0</v>
       </c>
@@ -1525,7 +1505,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
           <t>风险加权资产&gt;&gt;2024年12月31日</t>
@@ -1758,9 +1737,6 @@
           <t>其中:监管映射法</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>1</v>
       </c>
@@ -1846,9 +1822,6 @@
           <t>其中:现期风险暴露法</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>1</v>
       </c>
@@ -1859,9 +1832,6 @@
           <t>其中:其他方法</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>1</v>
       </c>
@@ -2022,9 +1992,6 @@
           <t>其中:资产证券化内部评级法</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>1</v>
       </c>
@@ -2135,9 +2102,6 @@
           <t>其中:内部模型法</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>1</v>
       </c>
@@ -2148,9 +2112,6 @@
           <t>其中:简化标准法</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>1</v>
       </c>
@@ -2281,7 +2242,6 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
           <t>a&gt;&gt;数额&gt;&gt;2024年12月31日</t>
@@ -2349,8 +2309,6 @@
           <t>核心一级资本</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -2386,7 +2344,6 @@
           <t>2,718,849</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>1</v>
       </c>
@@ -2462,7 +2419,6 @@
           <t>65,136</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>1</v>
       </c>
@@ -2478,7 +2434,6 @@
           <t>3,703</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>1</v>
       </c>
@@ -2494,7 +2449,6 @@
           <t>3,173,309</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>1</v>
       </c>
@@ -2505,8 +2459,6 @@
           <t>核心一级资本:扣除项</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>1</v>
       </c>
@@ -2517,8 +2469,6 @@
           <t>6&gt;&gt;审慎估值调整&gt;&gt;审慎估值调整</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>1</v>
       </c>
@@ -2569,8 +2519,6 @@
           <t>9&gt;&gt;依赖未来盈利的由经营亏损引起的净递延税资产&gt;&gt;依赖未来盈利的由经营亏损引起的净递延税资产</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>1</v>
       </c>
@@ -2586,7 +2534,6 @@
           <t>581</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
         <v>1</v>
       </c>
@@ -2597,8 +2544,6 @@
           <t>11&gt;&gt;损失准备缺口&gt;&gt;损失准备缺☐</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
         <v>1</v>
       </c>
@@ -2609,8 +2554,6 @@
           <t>12&gt;&gt;资产证券化销售利得&gt;&gt;资产证券化销售利得</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>1</v>
       </c>
@@ -2621,8 +2564,6 @@
           <t>13&gt;&gt;自身信用风险变化导致其负债公允价值变化带来的未实现损益&gt;&gt;自身信用风险变化导致其负债公允价值变化带来的未实现 损益</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>1</v>
       </c>
@@ -2633,8 +2574,6 @@
           <t>14&gt;&gt;确定受益类的养老金资产净额(扣除递延税项负债) 直接或间接持有本银行的股票</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
         <v>1</v>
       </c>
@@ -2645,8 +2584,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>1</v>
       </c>
@@ -2657,8 +2594,6 @@
           <t>16&gt;&gt;银行间或银行与其他金融机构间通过协议相互持有的核心一级资本&gt;&gt;银行间或银行与其他金融机构间通过协议相互持有的核心 一级资本</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
         <v>1</v>
       </c>
@@ -2669,8 +2604,6 @@
           <t>17&gt;&gt;对未并表金融机构小额少数资本投资中的核心一级资本中应扣除金额&gt;&gt;对未并表金融机构小额少数资本投资中的核心一级资本中 应扣除金额</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
         <v>1</v>
       </c>
@@ -2681,8 +2614,6 @@
           <t>18&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本中应扣除金额&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本中 应扣除金额</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
         <v>1</v>
       </c>
@@ -2693,8 +2624,6 @@
           <t>19&gt;&gt;其他依赖于银行未来盈利的净递延税资产中应扣除金额&gt;&gt;其他依赖于银行未来盈利的净递延税资产中应扣除金额</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
         <v>1</v>
       </c>
@@ -2705,8 +2634,6 @@
           <t>20&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本和其他依赖于银行未来盈利的净递延税资产的未扣除部分超过核心一级资本15%的应扣除金额&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本和 其他依赖于银行未来盈利的净递延税资产的未扣除部分超 过核心一级资本15%的应扣除金额</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
         <v>1</v>
       </c>
@@ -2717,8 +2644,6 @@
           <t>21&gt;&gt;其中:对金融机构大额少数资本投资中应扣除的金额&gt;&gt;其中:对金融机构大额少数资本投资中应扣除的金额</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
         <v>1</v>
       </c>

--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -481,12 +481,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31</t>
+          <t>2024年 12 月 31日</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024 年 9 月 30 词讼</t>
+          <t>2024 年 9 月 30 日</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
+          <t>哈行哈哈哈哈风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
         </is>
       </c>
       <c r="B9" t="n">

--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -481,12 +481,12 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31日</t>
+          <t>2024年 12 月 31大象</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024 年 9 月 30 日</t>
+          <t>2024 年 9 月 30 大大大</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>哈行哈哈哈哈风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
         </is>
       </c>
       <c r="B9" t="n">

--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -1,43 +1,379 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20805" windowHeight="10260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="P005_监管并表关键审慎监管指标" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P006_2024年度资本管理第三支柱信息披露报告" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="P009_风险加权资产概况" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="P010_资本构成" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P005_监管并表关键审慎监管指标" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P006_2024年度资本管理第三支柱信息披露报告" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P009_风险加权资产概况" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P010_资本构成" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,15 +381,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -406,7 +1032,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -416,8 +1041,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T43"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr"/>
@@ -448,6 +1073,18 @@
       </c>
       <c r="G1" t="inlineStr"/>
       <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -471,22 +1108,36 @@
           <t>d</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31大象</t>
+          <t>2024年 12 月 31代打</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024 年 9 月 30 大大大</t>
+          <t>2024 年 9 月 30 大小象</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -499,11 +1150,25 @@
           <t>2024 年 3 月 31 日</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -511,11 +1176,25 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -523,23 +1202,45 @@
           <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>3165549</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3124043</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3038387</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3045754</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3165549000000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3124043</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3038387</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3045754</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -547,23 +1248,45 @@
           <t>可用资本(数额)&gt;&gt;一级资本净额</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>3324424</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3322954</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3237254</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3245824</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3324424</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3322954</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3237254</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3245824</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -571,23 +1294,45 @@
           <t>可用资本(数额)&gt;&gt;资本净额</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>4303263</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4285564</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4175087</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4175290</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4303263</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4285564</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4175087</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4175290</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -595,11 +1340,25 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -607,23 +1366,45 @@
           <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>21854590</v>
-      </c>
-      <c r="C9" t="n">
-        <v>22150555</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21690492</v>
-      </c>
-      <c r="E9" t="n">
-        <v>21586165</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>21854590</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>22150555</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21690492</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21586165</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -631,23 +1412,45 @@
           <t>风险加权资产(数额)&gt;&gt;风险加权资产合计(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>21854590</v>
-      </c>
-      <c r="C10" t="n">
-        <v>22150555</v>
-      </c>
-      <c r="D10" t="n">
-        <v>21690492</v>
-      </c>
-      <c r="E10" t="n">
-        <v>21586165</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21854590</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22150555</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21690492</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21586165</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -655,11 +1458,25 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>0</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -667,23 +1484,45 @@
           <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="C12" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="E12" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14.48</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>14.01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -691,23 +1530,45 @@
           <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="C13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>14.11</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14.48</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14.01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -715,23 +1576,45 @@
           <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="C14" t="n">
-        <v>15</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="E14" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -739,23 +1622,45 @@
           <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>15.21</v>
-      </c>
-      <c r="C15" t="n">
-        <v>15</v>
-      </c>
-      <c r="D15" t="n">
-        <v>14.92</v>
-      </c>
-      <c r="E15" t="n">
-        <v>15.04</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -763,23 +1668,45 @@
           <t>资本充足率&gt;&gt;资本充足率(%)</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="C16" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="E16" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19.35</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>19.34</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -787,23 +1714,45 @@
           <t>资本充足率&gt;&gt;资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="C17" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="D17" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="E17" t="n">
-        <v>19.34</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19.35</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19.34</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -811,11 +1760,25 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -823,23 +1786,45 @@
           <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -847,23 +1832,45 @@
           <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -871,23 +1878,45 @@
           <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -895,23 +1924,45 @@
           <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>4</v>
-      </c>
-      <c r="C22" t="n">
-        <v>4</v>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -919,23 +1970,45 @@
           <t>其他各级资本要求&gt;&gt;满足最低资本要求后的可用核心一级资本净额占风险加权资产的比例(%)</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="C23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="E23" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9.21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.92</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -943,11 +2016,25 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
-        <v>0</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -955,17 +2042,25 @@
           <t>列标记</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -974,6 +2069,18 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -984,6 +2091,18 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -994,6 +2113,18 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1004,6 +2135,18 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1014,6 +2157,18 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -1024,6 +2179,18 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -1034,6 +2201,282 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1047,7 +2490,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -1502,7 +2945,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -2239,7 +3682,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">

--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1076,15 +1076,6 @@
       <c r="I1" t="inlineStr"/>
       <c r="J1" t="inlineStr"/>
       <c r="K1" t="inlineStr"/>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -1118,21 +1109,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31代打</t>
+          <t>2024年 12 月 31代妈妈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1160,15 +1142,6 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1186,25 +1159,16 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>可用资本(数额)&gt;&gt;核心一级资本净额</t>
+          <t>哈哈哈哈可用资本(数额)&gt;&gt;核心一级资本净额</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3165549000000</t>
+          <t>3165549000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1232,15 +1196,6 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1278,15 +1233,6 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1324,15 +1270,6 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1350,15 +1287,6 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1396,15 +1324,6 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1442,15 +1361,6 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1468,15 +1378,6 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1514,15 +1415,6 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1560,15 +1452,6 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1606,15 +1489,6 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1652,15 +1526,6 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1698,15 +1563,6 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1744,15 +1600,6 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1770,15 +1617,6 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1816,15 +1654,6 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1862,15 +1691,6 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1908,15 +1728,6 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1954,15 +1765,6 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2000,15 +1802,6 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -2026,15 +1819,6 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2072,15 +1856,6 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -2094,15 +1869,6 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -2116,15 +1882,6 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2138,15 +1895,6 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2160,15 +1908,6 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2182,15 +1921,6 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2204,15 +1934,6 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2226,15 +1947,6 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2248,15 +1960,6 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2270,213 +1973,6 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
+++ b/data/backend/static/excel_data/e57dd6ba-93f0-4dfb-85c9-7d417eeae589/e57dd6ba-93f0-4dfb-85c9-7d417eeae589_合并_20251224_210244.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20805" windowHeight="10260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P005_监管并表关键审慎监管指标" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P006_2024年度资本管理第三支柱信息披露报告" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P009_风险加权资产概况" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P010_资本构成" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="P006_2024年度资本管理第三支柱信息披露报告" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P009_风险加权资产概况" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="P010_资本构成" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="P005_监管并表关键审慎监管指标" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1041,29 +1041,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr"/>
       <c r="B1" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年12月31日</t>
+          <t>2024年&gt;&gt;12月31日</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年9月30日</t>
+          <t>2024年&gt;&gt;9月30日</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>c&gt;&gt;2024年6月30日</t>
+          <t>2024年&gt;&gt;6月30日</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>d&gt;&gt;2024年3月31日</t>
+          <t>2024年&gt;&gt;3月31日</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1073,9 +1073,6 @@
       </c>
       <c r="G1" t="inlineStr"/>
       <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
-      <c r="K1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -1099,507 +1096,353 @@
           <t>d</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024年 12 月 31代妈妈</t>
+          <t>2024年 12 月 31 大大大</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024 年 9 月 30 大小象</t>
+          <t>2024年 9 月 30日</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024 年 6 月 30 日</t>
+          <t>2024年 6 月 30日</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024 年 3 月 31 日</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>2024年 3 月 31日</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>调整后表内外资产余额</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42755544</v>
+      </c>
+      <c r="C4" t="n">
+        <v>42815730</v>
+      </c>
+      <c r="D4" t="n">
+        <v>42314726</v>
+      </c>
+      <c r="E4" t="n">
+        <v>41837451</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>哈哈哈哈可用资本(数额)&gt;&gt;核心一级资本净额</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3165549000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3124043</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3038387</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3045754</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>杠杆率(%)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3324424</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3322954</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3237254</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3245824</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>杠杆率a(%)1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>可用资本(数额)&gt;&gt;资本净额</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4303263</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4285564</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4175087</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4175290</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>杠杆率b(%)2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>杠杆率c(%)3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21854590</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>22150555</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>21690492</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>21586165</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计(应用资本底线前)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>21854590</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>22150555</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>21690492</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>21586165</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6237408</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6148940</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6115852</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6059382</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4957733</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5119129</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4877791</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4510003</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>流动性覆盖率(%)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="C12" t="n">
+        <v>120.29</v>
+      </c>
+      <c r="D12" t="n">
+        <v>125.43</v>
+      </c>
+      <c r="E12" t="n">
+        <v>134.46</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>可用稳定资金合计</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>28158322</v>
+      </c>
+      <c r="C14" t="n">
+        <v>28350638</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28236945</v>
+      </c>
+      <c r="E14" t="n">
+        <v>28350972</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>15.21</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>15.04</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>所需稳定资金合计</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>21027700</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20928125</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20917739</v>
+      </c>
+      <c r="E15" t="n">
+        <v>22174688</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;资本充足率(%)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>净稳定资金比例(%)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>133.91</v>
+      </c>
+      <c r="C16" t="n">
+        <v>135.47</v>
+      </c>
+      <c r="D16" t="n">
+        <v>134.99</v>
+      </c>
+      <c r="E16" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>资本充足率&gt;&gt;资本充足率(%)(应用资本底线前)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>19.35</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>19.25</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>19.34</t>
-        </is>
+          <t>列标记</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1607,372 +1450,59 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>其他各级资本要求&gt;&gt;满足最低资本要求后的可用核心一级资本净额占风险加权资产的比例(%)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>9.21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>8.92</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>9.04</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>列标记</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1985,31 +1515,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;12月31日</t>
+          <t>风险加权资产&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;9月30日</t>
+          <t>风险加权资产&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2024年&gt;&gt;6月30日</t>
+          <t>最低资本要求&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>2024年&gt;&gt;3月31日</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
         <is>
           <t>行标记</t>
         </is>
@@ -2031,399 +1556,686 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
+          <t>风险加权资产</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>最低资本要求</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
           <t>2024年 12 月 31 日</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2024年 9 月 30日</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2024年 6 月 30日</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024年 3 月 31日</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2024年 12 月 31 日</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>调整后表内外资产余额</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>42,755,544</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>42,815,730</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>42,314,726</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>41,837,451</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杠杆率(%)</t>
+          <t>信用风险</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>19,814,943</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>20,185,885</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+          <t>1,585,195</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>杠杆率a(%)1</t>
+          <t>信用风险（不包括交易对手信用风险、信用估值调整风险、银行账簿资产管理产品和银行账簿资产证券化）</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>19,433,391</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>19,818,263</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>7.76</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+          <t>1,554,670</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>杠杆率b(%)2</t>
+          <t>其中:权重法</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>5,820,738</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>5,596,995</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+          <t>465,658</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>杠杆率c(%)3</t>
+          <t>其中:证券、商品、外汇交易清算过程中形成的风险暴露</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>7.73</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="F9" t="n">
-        <v>0</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>其中:门槛扣除项中未扣除部分</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>363,177</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>369,459</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>29,054</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>合格优质流动性资产</t>
+          <t>其中:初级内部评级法</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6,237,408</t>
+          <t>11,323,706</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6,148,940</t>
+          <t>11,946,337</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6,115,852</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>6,059,382</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+          <t>905,896</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>现金净流出量</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4,957,733</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5,119,129</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4,877,791</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4,510,003</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+          <t>其中:监管映射法</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>流动性覆盖率(%)</t>
+          <t>其中:高级内部评级法</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>125.73</t>
+          <t>2,288,947</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>120.29</t>
+          <t>2,274,931</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>125.43</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>134.46</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
+          <t>183,116</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="F13" t="n">
-        <v>0</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>交易对手信用风险</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>117,100</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>115,575</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,368</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>可用稳定资金合计</t>
+          <t>其中:标准法</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>28,158,322</t>
+          <t>117,100</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28,350,638</t>
+          <t>115,575</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28,236,945</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>28,350,972</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
+          <t>9,368</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>所需稳定资金合计</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>21,027,700</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20,928,125</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>20,917,739</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>22,174,688</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
+          <t>其中:现期风险暴露法</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>净稳定资金比例(%)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>133.91</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>135.47</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>134.99</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>127.85</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
+          <t>其中:其他方法</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>信用估值调整风险</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>46,944</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>36,447</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3,756</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>银行账簿资产管理产品</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>199,861</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>197,318</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>15,989</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>其中:穿透法</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2,873</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1,910</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>其中:授权基础法</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>192,913</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>195,293</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>15,433</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>其中:适用1250%风险权重</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4,075</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>银行账簿资产证券化1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>17,647</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>18,282</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1,412</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>其中:资产证券化内部评级法</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>其中:资产证券化外部评级法</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>其中:资产证券化标准法</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7,818</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7,813</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>市场风险</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>250,577</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>194,481</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20,046</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>其中:标准法</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>250,577</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>194,481</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20,046</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>其中:内部模型法</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>其中:简化标准法</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>交易账簿和银行账簿间转换的资本要求</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>44,651</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3,572</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>操作风险</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1,744,419</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1,770,189</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>139,554</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>因应用资本底线而导致的额外调整</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21,854,590</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>22,150,555 1,748,367</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>列标记</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
         </is>
@@ -2440,32 +2252,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>风险加权资产&gt;&gt;2024年12月31日</t>
+          <t>a&gt;&gt;数额&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>风险加权资产&gt;&gt;2024年9月30日</t>
+          <t>b&gt;&gt;代码</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>最低资本要求&gt;&gt;2024年12月31日</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>行标记</t>
         </is>
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>a</t>
@@ -2476,691 +2288,393 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>风险加权资产</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>最低资本要求</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+          <t>数额</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024年 12 月 31 日</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2024年 9 月 30日</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2024年 12 月 31 日</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+          <t>2024年12月31日</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>信用风险</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>19,814,943</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>20,185,885</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1,585,195</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
+          <t>核心一级资本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>信用风险（不包括交易对手信用风险、信用估值调整风险、银行账簿资产管理产品和银行账簿资产证券化）</t>
+          <t>1&gt;&gt;实收资本和资本公积可计入部分&gt;&gt;实收资本和资本公积可计入部分</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19,433,391</t>
+          <t>385,621</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19,818,263</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1,554,670</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+          <t>e+g</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>其中:权重法</t>
+          <t>2&gt;&gt;留存收益&gt;&gt;留存收益</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,820,738</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5,596,995</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>465,658</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+          <t>2,718,849</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>其中:证券、商品、外汇交易清算过程中形成的风险暴露</t>
+          <t>2a&gt;&gt;盈余公积&gt;&gt;盈余公积</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>402,196</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+          <t>h</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>其中:门槛扣除项中未扣除部分</t>
+          <t>2b&gt;&gt;一般风险准备&gt;&gt;一般风险准备</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>363,177</t>
+          <t>534,151</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>369,459</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>29,054</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+          <t>一.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>其中:初级内部评级法</t>
+          <t>2c&gt;&gt;未分配利润&gt;&gt;未分配利润</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11,323,706</t>
+          <t>1,782,502</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11,946,337</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>905,896</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+          <t>J</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>其中:监管映射法</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+          <t>3&gt;&gt;累计其他综合收益&gt;&gt;累计其他综合收益</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>65,136</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>其中:高级内部评级法</t>
+          <t>4&gt;&gt;少数股东资本可计入部分&gt;&gt;少数股东资本可计入部分</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2,288,947</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2,274,931</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>183,116</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+          <t>3,703</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>交易对手信用风险</t>
+          <t>5&gt;&gt;扣除前的核心一级资本&gt;&gt;扣除前的核心一级资本</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>117,100</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>115,575</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>9,368</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+          <t>3,173,309</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>其中:标准法</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>117,100</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>115,575</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>9,368</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+          <t>核心一级资本:扣除项</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>其中:现期风险暴露法</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+          <t>6&gt;&gt;审慎估值调整&gt;&gt;审慎估值调整</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>其中:其他方法</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+          <t>7&gt;&gt;商誉(扣除递延税负债)&gt;&gt;商誉(扣除递延税负债)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2,170</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>a-C</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>信用估值调整风险</t>
+          <t>8&gt;&gt;其他无形资产(土地使用权除外)(扣除递延税负债)&gt;&gt;其他无形资产(土地使用权除外)(扣除递延税负债)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>46,944</t>
+          <t>5,009</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>36,447</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3,756</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+          <t>b-d</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>银行账簿资产管理产品</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>199,861</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>197,318</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>15,989</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+          <t>9&gt;&gt;依赖未来盈利的由经营亏损引起的净递延税资产&gt;&gt;依赖未来盈利的由经营亏损引起的净递延税资产</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>其中:穿透法</t>
+          <t>10&gt;&gt;对未按公允价值计量的项目进行套期形成的现金流储备&gt;&gt;对未按公允价值计量的项目进行套期形成的现金流储备</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2,873</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1,910</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+          <t>581</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>其中:授权基础法</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>192,913</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>195,293</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>15,433</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
+          <t>11&gt;&gt;损失准备缺口&gt;&gt;损失准备缺☐</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>其中:适用1250%风险权重</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>4,075</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
+          <t>12&gt;&gt;资产证券化销售利得&gt;&gt;资产证券化销售利得</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>银行账簿资产证券化1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>17,647</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>18,282</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1,412</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
+          <t>13&gt;&gt;自身信用风险变化导致其负债公允价值变化带来的未实现损益&gt;&gt;自身信用风险变化导致其负债公允价值变化带来的未实现 损益</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>其中:资产证券化内部评级法</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
+          <t>14&gt;&gt;确定受益类的养老金资产净额(扣除递延税项负债) 直接或间接持有本银行的股票</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>其中:资产证券化外部评级法</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>其中:资产证券化标准法</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>7,818</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>7,813</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
+          <t>16&gt;&gt;银行间或银行与其他金融机构间通过协议相互持有的核心一级资本&gt;&gt;银行间或银行与其他金融机构间通过协议相互持有的核心 一级资本</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>市场风险</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>250,577</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>194,481</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>20,046</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
+          <t>17&gt;&gt;对未并表金融机构小额少数资本投资中的核心一级资本中应扣除金额&gt;&gt;对未并表金融机构小额少数资本投资中的核心一级资本中 应扣除金额</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>其中:标准法</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>250,577</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>194,481</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>20,046</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
+          <t>18&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本中应扣除金额&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本中 应扣除金额</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>其中:内部模型法</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
+          <t>19&gt;&gt;其他依赖于银行未来盈利的净递延税资产中应扣除金额&gt;&gt;其他依赖于银行未来盈利的净递延税资产中应扣除金额</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>其中:简化标准法</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
+          <t>20&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本和其他依赖于银行未来盈利的净递延税资产的未扣除部分超过核心一级资本15%的应扣除金额&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本和 其他依赖于银行未来盈利的净递延税资产的未扣除部分超 过核心一级资本15%的应扣除金额</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>交易账簿和银行账簿间转换的资本要求</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>44,651</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>3,572</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
+          <t>21&gt;&gt;其中:对金融机构大额少数资本投资中应扣除的金额&gt;&gt;其中:对金融机构大额少数资本投资中应扣除的金额</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>操作风险</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1,744,419</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1,770,189</t>
-        </is>
+          <t>列标记</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
-        <is>
-          <t>139,554</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>因应用资本底线而导致的额外调整</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21,854,590</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>22,150,555 1,748,367</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>列标记</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
         <is>
           <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
         </is>
@@ -3177,32 +2691,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>a&gt;&gt;数额&gt;&gt;2024年12月31日</t>
+          <t>a&gt;&gt;2024年12月31日</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>b&gt;&gt;代码</t>
+          <t>b&gt;&gt;2024年9月30日</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>c&gt;&gt;2024年6月30日</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>d&gt;&gt;2024年3月31日</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>行标记</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>(人民币百万元,百分比除外)</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>a</t>
@@ -3213,393 +2732,623 @@
           <t>b</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>数额</t>
+          <t>2024年 12 月 31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+          <t>2024 年 9 月 30 日</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024 年 6 月 30 日</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024 年 3 月 31 日</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024年12月31日</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>核心一级资本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+          <t>哈哈哈哈可用资本(数额)&gt;&gt;核心一级资本净额</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3165549000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3124043</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3038387</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3045754</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1&gt;&gt;实收资本和资本公积可计入部分&gt;&gt;实收资本和资本公积可计入部分</t>
+          <t>可用资本(数额)&gt;&gt;一级资本净额</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>385,621</t>
+          <t>3324424</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>e+g</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
+          <t>3322954</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3237254</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3245824</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2&gt;&gt;留存收益&gt;&gt;留存收益</t>
+          <t>可用资本(数额)&gt;&gt;资本净额</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2,718,849</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
+          <t>4303263</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4285564</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4175087</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4175290</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2a&gt;&gt;盈余公积&gt;&gt;盈余公积</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>402,196</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2b&gt;&gt;一般风险准备&gt;&gt;一般风险准备</t>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>534,151</t>
+          <t>21854590</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>一.</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
+          <t>22150555</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21690492</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21586165</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2c&gt;&gt;未分配利润&gt;&gt;未分配利润</t>
+          <t>风险加权资产(数额)&gt;&gt;风险加权资产合计(应用资本底线前)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1,782,502</t>
+          <t>21854590</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
+          <t>22150555</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21690492</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21586165</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3&gt;&gt;累计其他综合收益&gt;&gt;累计其他综合收益</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>65,136</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4&gt;&gt;少数股东资本可计入部分&gt;&gt;少数股东资本可计入部分</t>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3,703</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
+          <t>14.48</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>14.01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5&gt;&gt;扣除前的核心一级资本&gt;&gt;扣除前的核心一级资本</t>
+          <t>资本充足率&gt;&gt;核心一级资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3,173,309</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
+          <t>14.48</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>14.01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>核心一级资本:扣除项</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6&gt;&gt;审慎估值调整&gt;&gt;审慎估值调整</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
+          <t>资本充足率&gt;&gt;一级资本充足率(%)(应用资本底线前)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15.21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>14.92</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>15.04</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7&gt;&gt;商誉(扣除递延税负债)&gt;&gt;商誉(扣除递延税负债)</t>
+          <t>资本充足率&gt;&gt;资本充足率(%)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2,170</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>a-C</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
+          <t>19.35</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>19.34</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8&gt;&gt;其他无形资产(土地使用权除外)(扣除递延税负债)&gt;&gt;其他无形资产(土地使用权除外)(扣除递延税负债)</t>
+          <t>资本充足率&gt;&gt;资本充足率(%)(应用资本底线前)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,009</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>b-d</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
+          <t>19.35</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>19.25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19.34</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>9&gt;&gt;依赖未来盈利的由经营亏损引起的净递延税资产&gt;&gt;依赖未来盈利的由经营亏损引起的净递延税资产</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10&gt;&gt;对未按公允价值计量的项目进行套期形成的现金流储备&gt;&gt;对未按公允价值计量的项目进行套期形成的现金流储备</t>
+          <t>其他各级资本要求&gt;&gt;储备资本要求(%)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11&gt;&gt;损失准备缺口&gt;&gt;损失准备缺☐</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
+          <t>其他各级资本要求&gt;&gt;逆周期资本要求(%)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12&gt;&gt;资产证券化销售利得&gt;&gt;资产证券化销售利得</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
+          <t>其他各级资本要求&gt;&gt;全球系统重要性银行或国内系统重要性银行附加资本要求(%)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13&gt;&gt;自身信用风险变化导致其负债公允价值变化带来的未实现损益&gt;&gt;自身信用风险变化导致其负债公允价值变化带来的未实现 损益</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
+          <t>其他各级资本要求&gt;&gt;其他各级资本要求(%)(8+9+10)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14&gt;&gt;确定受益类的养老金资产净额(扣除递延税项负债) 直接或间接持有本银行的股票</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
+          <t>其他各级资本要求&gt;&gt;满足最低资本要求后的可用核心一级资本净额占风险加权资产的比例(%)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9.21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.92</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9.04</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>16&gt;&gt;银行间或银行与其他金融机构间通过协议相互持有的核心一级资本&gt;&gt;银行间或银行与其他金融机构间通过协议相互持有的核心 一级资本</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>17&gt;&gt;对未并表金融机构小额少数资本投资中的核心一级资本中应扣除金额&gt;&gt;对未并表金融机构小额少数资本投资中的核心一级资本中 应扣除金额</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>18&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本中应扣除金额&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本中 应扣除金额</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>19&gt;&gt;其他依赖于银行未来盈利的净递延税资产中应扣除金额&gt;&gt;其他依赖于银行未来盈利的净递延税资产中应扣除金额</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本和其他依赖于银行未来盈利的净递延税资产的未扣除部分超过核心一级资本15%的应扣除金额&gt;&gt;对未并表金融机构大额少数资本投资中的核心一级资本和 其他依赖于银行未来盈利的净递延税资产的未扣除部分超 过核心一级资本15%的应扣除金额</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>21&gt;&gt;其中:对金融机构大额少数资本投资中应扣除的金额&gt;&gt;其中:对金融机构大额少数资本投资中应扣除的金额</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
           <t>列标记</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记说明:0-纯文本 1-标准数值 2-格式问题 3-可能错误 4-混合类型</t>
         </is>
